--- a/salidas/empresas/PYPL.xlsx
+++ b/salidas/empresas/PYPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B2" t="n">
-        <v>38.27317810058594</v>
+        <v>38.27318572998047</v>
       </c>
       <c r="C2" t="n">
         <v>38.70000076293945</v>
@@ -507,7 +519,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B3" t="n">
@@ -532,11 +544,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B4" t="n">
-        <v>30.69766235351562</v>
+        <v>30.69766426086426</v>
       </c>
       <c r="C4" t="n">
         <v>31.04000091552734</v>
@@ -557,11 +569,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B5" t="n">
-        <v>35.61285018920898</v>
+        <v>35.61284637451172</v>
       </c>
       <c r="C5" t="n">
         <v>36.0099983215332</v>
@@ -582,7 +594,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B6" t="n">
@@ -607,7 +619,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B7" t="n">
@@ -632,7 +644,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B8" t="n">
@@ -657,7 +669,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B9" t="n">
@@ -686,7 +698,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B10" t="n">
@@ -715,7 +727,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B11" t="n">
@@ -744,7 +756,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B12" t="n">
@@ -773,11 +785,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B13" t="n">
-        <v>36.10733413696289</v>
+        <v>36.10733795166016</v>
       </c>
       <c r="C13" t="n">
         <v>36.5099983215332</v>
@@ -802,7 +814,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B14" t="n">
@@ -831,11 +843,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B15" t="n">
-        <v>36.74028015136719</v>
+        <v>36.74028396606445</v>
       </c>
       <c r="C15" t="n">
         <v>37.15000152587891</v>
@@ -860,7 +872,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B16" t="n">
@@ -889,11 +901,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B17" t="n">
-        <v>41.20053863525391</v>
+        <v>41.20053482055664</v>
       </c>
       <c r="C17" t="n">
         <v>41.65999984741211</v>
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B18" t="n">
@@ -947,11 +959,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B19" t="n">
-        <v>39.03469085693359</v>
+        <v>39.03468704223633</v>
       </c>
       <c r="C19" t="n">
         <v>39.47000122070312</v>
@@ -976,7 +988,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B20" t="n">
@@ -1005,7 +1017,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B21" t="n">
@@ -1034,7 +1046,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B22" t="n">
@@ -1063,11 +1075,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B23" t="n">
-        <v>47.19369888305664</v>
+        <v>47.19370269775391</v>
       </c>
       <c r="C23" t="n">
         <v>47.72000122070312</v>
@@ -1092,7 +1104,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B24" t="n">
@@ -1121,11 +1133,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B25" t="n">
-        <v>53.07807540893555</v>
+        <v>53.07807922363281</v>
       </c>
       <c r="C25" t="n">
         <v>53.66999816894531</v>
@@ -1150,11 +1162,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B26" t="n">
-        <v>57.90425872802734</v>
+        <v>57.90425491333008</v>
       </c>
       <c r="C26" t="n">
         <v>58.54999923706055</v>
@@ -1179,7 +1191,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B27" t="n">
@@ -1208,7 +1220,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B28" t="n">
@@ -1237,11 +1249,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B29" t="n">
-        <v>71.75974273681641</v>
+        <v>71.75973510742188</v>
       </c>
       <c r="C29" t="n">
         <v>72.55999755859375</v>
@@ -1266,11 +1278,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B30" t="n">
-        <v>74.89479064941406</v>
+        <v>74.894775390625</v>
       </c>
       <c r="C30" t="n">
         <v>75.73000335693359</v>
@@ -1295,7 +1307,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B31" t="n">
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B32" t="n">
@@ -1353,11 +1365,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B33" t="n">
-        <v>78.53419494628906</v>
+        <v>78.53420257568359</v>
       </c>
       <c r="C33" t="n">
         <v>79.41000366210938</v>
@@ -1382,11 +1394,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B34" t="n">
-        <v>75.03324890136719</v>
+        <v>75.03323364257812</v>
       </c>
       <c r="C34" t="n">
         <v>75.87000274658203</v>
@@ -1411,11 +1423,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B35" t="n">
-        <v>73.78712463378906</v>
+        <v>73.78713226318359</v>
       </c>
       <c r="C35" t="n">
         <v>74.61000061035156</v>
@@ -1440,7 +1452,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B36" t="n">
@@ -1469,7 +1481,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B37" t="n">
@@ -1498,7 +1510,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B38" t="n">
@@ -1527,11 +1539,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B39" t="n">
-        <v>91.31170654296875</v>
+        <v>91.31169891357422</v>
       </c>
       <c r="C39" t="n">
         <v>92.33000183105469</v>
@@ -1556,11 +1568,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B40" t="n">
-        <v>86.87122344970703</v>
+        <v>86.8712158203125</v>
       </c>
       <c r="C40" t="n">
         <v>87.83999633789062</v>
@@ -1585,7 +1597,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B41" t="n">
@@ -1614,7 +1626,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B42" t="n">
@@ -1643,7 +1655,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B43" t="n">
@@ -1672,11 +1684,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B44" t="n">
-        <v>87.78108215332031</v>
+        <v>87.78107452392578</v>
       </c>
       <c r="C44" t="n">
         <v>88.76000213623047</v>
@@ -1701,11 +1713,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B45" t="n">
-        <v>96.98839569091797</v>
+        <v>96.9884033203125</v>
       </c>
       <c r="C45" t="n">
         <v>98.06999969482422</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B46" t="n">
-        <v>102.6947555541992</v>
+        <v>102.6947631835938</v>
       </c>
       <c r="C46" t="n">
         <v>103.8399963378906</v>
@@ -1759,11 +1771,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B47" t="n">
-        <v>111.5262756347656</v>
+        <v>111.5262680053711</v>
       </c>
       <c r="C47" t="n">
         <v>112.7699966430664</v>
@@ -1788,11 +1800,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B48" t="n">
-        <v>108.5395812988281</v>
+        <v>108.5395736694336</v>
       </c>
       <c r="C48" t="n">
         <v>109.75</v>
@@ -1817,11 +1829,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B49" t="n">
-        <v>113.197639465332</v>
+        <v>113.1976318359375</v>
       </c>
       <c r="C49" t="n">
         <v>114.4599990844727</v>
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B50" t="n">
@@ -1875,7 +1887,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B51" t="n">
@@ -1904,7 +1916,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B52" t="n">
@@ -1933,7 +1945,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B53" t="n">
@@ -1962,7 +1974,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B54" t="n">
@@ -1991,7 +2003,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B55" t="n">
@@ -2020,7 +2032,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B56" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B57" t="n">
@@ -2078,11 +2090,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B58" t="n">
-        <v>94.68408203125</v>
+        <v>94.68408966064453</v>
       </c>
       <c r="C58" t="n">
         <v>95.73999786376953</v>
@@ -2107,7 +2119,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B59" t="n">
@@ -2136,7 +2148,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B60" t="n">
@@ -2165,11 +2177,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B61" t="n">
-        <v>172.3084259033203</v>
+        <v>172.3084411621094</v>
       </c>
       <c r="C61" t="n">
         <v>174.2299957275391</v>
@@ -2194,7 +2206,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B62" t="n">
@@ -2223,7 +2235,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B63" t="n">
@@ -2252,7 +2264,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B64" t="n">
@@ -2281,7 +2293,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B65" t="n">
@@ -2310,7 +2322,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B66" t="n">
@@ -2339,11 +2351,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B67" t="n">
-        <v>231.6170349121094</v>
+        <v>231.6170196533203</v>
       </c>
       <c r="C67" t="n">
         <v>234.1999969482422</v>
@@ -2368,7 +2380,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B68" t="n">
@@ -2397,11 +2409,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B69" t="n">
-        <v>256.984130859375</v>
+        <v>256.9841613769531</v>
       </c>
       <c r="C69" t="n">
         <v>259.8500061035156</v>
@@ -2426,11 +2438,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B70" t="n">
-        <v>240.1617431640625</v>
+        <v>240.1617279052734</v>
       </c>
       <c r="C70" t="n">
         <v>242.8399963378906</v>
@@ -2455,7 +2467,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B71" t="n">
@@ -2484,11 +2496,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B72" t="n">
-        <v>257.1522216796875</v>
+        <v>257.1522827148438</v>
       </c>
       <c r="C72" t="n">
         <v>260.0199890136719</v>
@@ -2513,11 +2525,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B73" t="n">
-        <v>288.2652893066406</v>
+        <v>288.2653198242188</v>
       </c>
       <c r="C73" t="n">
         <v>291.4800109863281</v>
@@ -2542,11 +2554,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B74" t="n">
-        <v>272.4912109375</v>
+        <v>272.4911804199219</v>
       </c>
       <c r="C74" t="n">
         <v>275.5299987792969</v>
@@ -2571,7 +2583,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B75" t="n">
@@ -2600,7 +2612,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B76" t="n">
@@ -2629,7 +2641,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B77" t="n">
@@ -2658,11 +2670,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B78" t="n">
-        <v>182.8508758544922</v>
+        <v>182.8508605957031</v>
       </c>
       <c r="C78" t="n">
         <v>184.8899993896484</v>
@@ -2687,11 +2699,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B79" t="n">
-        <v>186.5001678466797</v>
+        <v>186.5001831054688</v>
       </c>
       <c r="C79" t="n">
         <v>188.5800018310547</v>
@@ -2716,7 +2728,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B80" t="n">
@@ -2745,11 +2757,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B81" t="n">
-        <v>110.6955337524414</v>
+        <v>110.6955413818359</v>
       </c>
       <c r="C81" t="n">
         <v>111.9300003051758</v>
@@ -2774,7 +2786,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B82" t="n">
@@ -2803,11 +2815,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B83" t="n">
-        <v>86.96022796630859</v>
+        <v>86.96022033691406</v>
       </c>
       <c r="C83" t="n">
         <v>87.93000030517578</v>
@@ -2832,11 +2844,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B84" t="n">
-        <v>84.27022552490234</v>
+        <v>84.27023315429688</v>
       </c>
       <c r="C84" t="n">
         <v>85.20999908447266</v>
@@ -2861,7 +2873,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B85" t="n">
@@ -2890,11 +2902,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B86" t="n">
-        <v>85.57566833496094</v>
+        <v>85.57567596435547</v>
       </c>
       <c r="C86" t="n">
         <v>86.52999877929688</v>
@@ -2919,7 +2931,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B87" t="n">
@@ -2948,11 +2960,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B88" t="n">
-        <v>85.12073516845703</v>
+        <v>85.12075042724609</v>
       </c>
       <c r="C88" t="n">
         <v>86.06999969482422</v>
@@ -2977,11 +2989,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B89" t="n">
-        <v>82.658203125</v>
+        <v>82.65819549560547</v>
       </c>
       <c r="C89" t="n">
         <v>83.58000183105469</v>
@@ -3006,11 +3018,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B90" t="n">
-        <v>77.54523468017578</v>
+        <v>77.54522705078125</v>
       </c>
       <c r="C90" t="n">
         <v>78.41000366210938</v>
@@ -3035,11 +3047,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B91" t="n">
-        <v>70.43451690673828</v>
+        <v>70.43452453613281</v>
       </c>
       <c r="C91" t="n">
         <v>71.22000122070312</v>
@@ -3064,11 +3076,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B92" t="n">
-        <v>80.59126281738281</v>
+        <v>80.59125518798828</v>
       </c>
       <c r="C92" t="n">
         <v>81.48999786376953</v>
@@ -3093,11 +3105,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B93" t="n">
-        <v>72.78827667236328</v>
+        <v>72.78826141357422</v>
       </c>
       <c r="C93" t="n">
         <v>73.59999847412109</v>
@@ -3122,7 +3134,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B94" t="n">
@@ -3151,11 +3163,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B95" t="n">
-        <v>75.16181182861328</v>
+        <v>75.16180419921875</v>
       </c>
       <c r="C95" t="n">
         <v>76</v>
@@ -3180,7 +3192,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B96" t="n">
@@ -3209,11 +3221,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B97" t="n">
-        <v>65.99404144287109</v>
+        <v>65.99404907226562</v>
       </c>
       <c r="C97" t="n">
         <v>66.73000335693359</v>
@@ -3238,11 +3250,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B98" t="n">
-        <v>74.98379516601562</v>
+        <v>74.98378753662109</v>
       </c>
       <c r="C98" t="n">
         <v>75.81999969482422</v>
@@ -3267,11 +3279,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B99" t="n">
-        <v>61.82057952880859</v>
+        <v>61.82058334350586</v>
       </c>
       <c r="C99" t="n">
         <v>62.5099983215332</v>
@@ -3296,7 +3308,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B100" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B101" t="n">
@@ -3354,7 +3366,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B102" t="n">
@@ -3383,7 +3395,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B103" t="n">
@@ -3412,11 +3424,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B104" t="n">
-        <v>60.67338180541992</v>
+        <v>60.67337417602539</v>
       </c>
       <c r="C104" t="n">
         <v>61.34999847412109</v>
@@ -3441,7 +3453,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B105" t="n">
@@ -3470,11 +3482,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B106" t="n">
-        <v>66.25117492675781</v>
+        <v>66.25116729736328</v>
       </c>
       <c r="C106" t="n">
         <v>66.98999786376953</v>
@@ -3499,11 +3511,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B107" t="n">
-        <v>67.17092132568359</v>
+        <v>67.17091369628906</v>
       </c>
       <c r="C107" t="n">
         <v>67.91999816894531</v>
@@ -3528,11 +3540,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B108" t="n">
-        <v>62.29529190063477</v>
+        <v>62.29529571533203</v>
       </c>
       <c r="C108" t="n">
         <v>62.9900016784668</v>
@@ -3557,7 +3569,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B109" t="n">
@@ -3586,7 +3598,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B110" t="n">
@@ -3615,11 +3627,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B111" t="n">
-        <v>71.63117980957031</v>
+        <v>71.63117218017578</v>
       </c>
       <c r="C111" t="n">
         <v>72.43000030517578</v>
@@ -3644,11 +3656,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B112" t="n">
-        <v>77.16941070556641</v>
+        <v>77.16941833496094</v>
       </c>
       <c r="C112" t="n">
         <v>78.02999877929688</v>
@@ -3673,11 +3685,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B113" t="n">
-        <v>78.4254150390625</v>
+        <v>78.42540740966797</v>
       </c>
       <c r="C113" t="n">
         <v>79.30000305175781</v>
@@ -3702,11 +3714,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B114" t="n">
-        <v>85.81301116943359</v>
+        <v>85.81301879882812</v>
       </c>
       <c r="C114" t="n">
         <v>86.76999664306641</v>
@@ -3731,7 +3743,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B115" t="n">
@@ -3760,7 +3772,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B116" t="n">
@@ -3789,7 +3801,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B117" t="n">
@@ -3818,7 +3830,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B118" t="n">
@@ -3847,11 +3859,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B119" t="n">
-        <v>65.11385345458984</v>
+        <v>65.11386108398438</v>
       </c>
       <c r="C119" t="n">
         <v>65.83999633789062</v>
@@ -3876,7 +3888,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B120" t="n">
@@ -3905,11 +3917,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B121" t="n">
-        <v>73.50032806396484</v>
+        <v>73.50033569335938</v>
       </c>
       <c r="C121" t="n">
         <v>74.31999969482422</v>
@@ -3934,11 +3946,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B122" t="n">
-        <v>68.00165557861328</v>
+        <v>68.00166320800781</v>
       </c>
       <c r="C122" t="n">
         <v>68.76000213623047</v>
@@ -3963,11 +3975,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B123" t="n">
-        <v>69.41588592529297</v>
+        <v>69.4158935546875</v>
       </c>
       <c r="C123" t="n">
         <v>70.19000244140625</v>
@@ -3992,11 +4004,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B124" t="n">
-        <v>66.32040405273438</v>
+        <v>66.32039642333984</v>
       </c>
       <c r="C124" t="n">
         <v>67.05999755859375</v>
@@ -4021,11 +4033,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B125" t="n">
-        <v>68.50601959228516</v>
+        <v>68.50602722167969</v>
       </c>
       <c r="C125" t="n">
         <v>69.26999664306641</v>
@@ -4050,11 +4062,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B126" t="n">
-        <v>62.14192199707031</v>
+        <v>62.14191818237305</v>
       </c>
       <c r="C126" t="n">
         <v>62.68999862670898</v>
@@ -4079,11 +4091,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B127" t="n">
-        <v>57.86960601806641</v>
+        <v>57.86960220336914</v>
       </c>
       <c r="C127" t="n">
         <v>58.38000106811523</v>
@@ -4108,7 +4120,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B128" t="n">
@@ -4137,7 +4149,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B129" t="n">
@@ -4166,7 +4178,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B130" t="n">
@@ -4195,11 +4207,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B131" t="n">
-        <v>49.85212326049805</v>
+        <v>49.85212707519531</v>
       </c>
       <c r="C131" t="n">
         <v>50.13999938964844</v>
@@ -4224,7 +4236,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B132" t="n">
@@ -4253,7 +4265,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B133" t="n">
@@ -4282,7 +4294,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B134" t="n">
@@ -4311,7 +4323,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B135" t="n">
@@ -4340,32 +4352,32 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B136" t="n">
-        <v>52.5099983215332</v>
+        <v>52.59999847412109</v>
       </c>
       <c r="C136" t="n">
-        <v>52.5099983215332</v>
+        <v>52.59999847412109</v>
       </c>
       <c r="D136" t="n">
-        <v>204528500</v>
+        <v>213061000</v>
       </c>
       <c r="E136" t="n">
         <v>5.290000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>9.926275675148052</v>
+        <v>9.943288936506821</v>
       </c>
       <c r="G136" t="n">
         <v>882105493</v>
       </c>
       <c r="H136" t="n">
-        <v>46319357956.84521</v>
+        <v>46398747585.81384</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2318639908979685</v>
+        <v>0.2415368702391699</v>
       </c>
     </row>
   </sheetData>
@@ -4397,75 +4409,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -4501,13 +4513,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -4543,13 +4555,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -4585,13 +4597,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -4618,7 +4630,7 @@
       <c r="I5" t="n">
         <v>0.34</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K5" t="n">
@@ -4631,13 +4643,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -4664,7 +4676,7 @@
       <c r="I6" t="n">
         <v>0.86</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K6" t="n">
@@ -4677,13 +4689,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4710,7 +4722,7 @@
       <c r="I7" t="n">
         <v>0.88</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K7" t="n">
@@ -4723,13 +4735,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4756,7 +4768,7 @@
       <c r="I8" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K8" t="n">
@@ -4769,13 +4781,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4802,7 +4814,7 @@
       <c r="I9" t="n">
         <v>1.01</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K9" t="n">
@@ -4815,13 +4827,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -4848,7 +4860,7 @@
       <c r="I10" t="n">
         <v>1.1</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K10" t="n">
@@ -4861,13 +4873,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -4894,7 +4906,7 @@
       <c r="I11" t="n">
         <v>1.12</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="K11" t="n">
@@ -4907,13 +4919,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -4940,7 +4952,7 @@
       <c r="I12" t="n">
         <v>1.14</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="K12" t="n">
@@ -4953,13 +4965,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -4986,7 +4998,7 @@
       <c r="I13" t="n">
         <v>1.16</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="K13" t="n">
@@ -4999,13 +5011,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -5032,7 +5044,7 @@
       <c r="I14" t="n">
         <v>1.18</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K14" t="n">
@@ -5045,13 +5057,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -5078,7 +5090,7 @@
       <c r="I15" t="n">
         <v>1.25</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K15" t="n">
@@ -5091,13 +5103,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -5124,7 +5136,7 @@
       <c r="I16" t="n">
         <v>1.29</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="K16" t="n">
@@ -5137,13 +5149,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -5170,7 +5182,7 @@
       <c r="I17" t="n">
         <v>1.47</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="K17" t="n">
@@ -5183,13 +5195,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -5216,7 +5228,7 @@
       <c r="I18" t="n">
         <v>1.57</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K18" t="n">
@@ -5229,13 +5241,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -5262,7 +5274,7 @@
       <c r="I19" t="n">
         <v>1.67</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K19" t="n">
@@ -5275,13 +5287,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -5308,7 +5320,7 @@
       <c r="I20" t="n">
         <v>1.72</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="K20" t="n">
@@ -5321,13 +5333,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -5354,7 +5366,7 @@
       <c r="I21" t="n">
         <v>1.71</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K21" t="n">
@@ -5367,13 +5379,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -5400,7 +5412,7 @@
       <c r="I22" t="n">
         <v>1.85</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K22" t="n">
@@ -5413,13 +5425,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -5446,7 +5458,7 @@
       <c r="I23" t="n">
         <v>2.1</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K23" t="n">
@@ -5459,13 +5471,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -5492,7 +5504,7 @@
       <c r="I24" t="n">
         <v>2.13</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K24" t="n">
@@ -5505,13 +5517,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -5538,7 +5550,7 @@
       <c r="I25" t="n">
         <v>2.07</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="K25" t="n">
@@ -5551,13 +5563,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -5584,7 +5596,7 @@
       <c r="I26" t="n">
         <v>1.58</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K26" t="n">
@@ -5597,13 +5609,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -5630,7 +5642,7 @@
       <c r="I27" t="n">
         <v>2.18</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K27" t="n">
@@ -5643,13 +5655,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -5676,7 +5688,7 @@
       <c r="I28" t="n">
         <v>2.65</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K28" t="n">
@@ -5689,13 +5701,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -5722,7 +5734,7 @@
       <c r="I29" t="n">
         <v>3.54</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="K29" t="n">
@@ -5735,13 +5747,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -5768,7 +5780,7 @@
       <c r="I30" t="n">
         <v>4.390000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K30" t="n">
@@ -5781,13 +5793,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -5814,7 +5826,7 @@
       <c r="I31" t="n">
         <v>4.100000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K31" t="n">
@@ -5827,13 +5839,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -5860,7 +5872,7 @@
       <c r="I32" t="n">
         <v>4.16</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="K32" t="n">
@@ -5873,13 +5885,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -5906,7 +5918,7 @@
       <c r="I33" t="n">
         <v>3.52</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="K33" t="n">
@@ -5919,13 +5931,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -5952,7 +5964,7 @@
       <c r="I34" t="n">
         <v>3.03</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K34" t="n">
@@ -5965,13 +5977,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -5998,7 +6010,7 @@
       <c r="I35" t="n">
         <v>1.74</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K35" t="n">
@@ -6011,13 +6023,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -6044,7 +6056,7 @@
       <c r="I36" t="n">
         <v>1.97</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K36" t="n">
@@ -6057,13 +6069,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -6090,7 +6102,7 @@
       <c r="I37" t="n">
         <v>2.09</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K37" t="n">
@@ -6103,13 +6115,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -6136,7 +6148,7 @@
       <c r="I38" t="n">
         <v>2.36</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="K38" t="n">
@@ -6149,13 +6161,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -6182,7 +6194,7 @@
       <c r="I39" t="n">
         <v>3.57</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K39" t="n">
@@ -6195,13 +6207,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -6228,7 +6240,7 @@
       <c r="I40" t="n">
         <v>3.35</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K40" t="n">
@@ -6241,13 +6253,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -6274,7 +6286,7 @@
       <c r="I41" t="n">
         <v>3.84</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="K41" t="n">
@@ -6287,13 +6299,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -6320,7 +6332,7 @@
       <c r="I42" t="n">
         <v>3.97</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K42" t="n">
@@ -6333,13 +6345,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -6366,7 +6378,7 @@
       <c r="I43" t="n">
         <v>4.13</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K43" t="n">
@@ -6379,13 +6391,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -6412,7 +6424,7 @@
       <c r="I44" t="n">
         <v>4.19</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="K44" t="n">
@@ -6425,13 +6437,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -6458,7 +6470,7 @@
       <c r="I45" t="n">
         <v>3.99</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="K45" t="n">
@@ -6471,13 +6483,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -6504,7 +6516,7 @@
       <c r="I46" t="n">
         <v>4.45</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K46" t="n">
@@ -6517,13 +6529,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -6550,7 +6562,7 @@
       <c r="I47" t="n">
         <v>4.66</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="K47" t="n">
@@ -6563,13 +6575,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -6596,7 +6608,7 @@
       <c r="I48" t="n">
         <v>4.970000000000001</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="K48" t="n">
@@ -6609,13 +6621,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -6642,7 +6654,7 @@
       <c r="I49" t="n">
         <v>5.41</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="K49" t="n">
@@ -6655,13 +6667,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -6688,7 +6700,7 @@
       <c r="I50" t="n">
         <v>5.33</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K50" t="n">
@@ -6701,13 +6713,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -6728,7 +6740,7 @@
       <c r="I51" t="n">
         <v>5.290000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K51" t="n">
@@ -6765,52 +6777,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42208</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C2" t="n">
@@ -6839,10 +6851,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C3" t="n">
@@ -6871,10 +6883,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42405</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C4" t="n">
@@ -6903,10 +6915,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42482</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C5" t="n">
@@ -6935,10 +6947,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42571</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>42577</v>
       </c>
       <c r="C6" t="n">
@@ -6967,10 +6979,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42662</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="C7" t="n">
@@ -6999,10 +7011,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42768</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="C8" t="n">
@@ -7031,10 +7043,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C9" t="n">
@@ -7063,10 +7075,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C10" t="n">
@@ -7095,10 +7107,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43026</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="C11" t="n">
@@ -7127,10 +7139,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43133</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="C12" t="n">
@@ -7159,10 +7171,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C13" t="n">
@@ -7191,10 +7203,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C14" t="n">
@@ -7223,10 +7235,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43390</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="C15" t="n">
@@ -7255,10 +7267,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C16" t="n">
@@ -7287,10 +7299,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43574</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C17" t="n">
@@ -7319,10 +7331,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C18" t="n">
@@ -7351,10 +7363,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C19" t="n">
@@ -7383,10 +7395,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="C20" t="n">
@@ -7415,10 +7427,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C21" t="n">
@@ -7447,10 +7459,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44036</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C22" t="n">
@@ -7479,10 +7491,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44132</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C23" t="n">
@@ -7511,10 +7523,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="C24" t="n">
@@ -7543,10 +7555,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C25" t="n">
@@ -7575,10 +7587,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C26" t="n">
@@ -7607,10 +7619,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44502</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="C27" t="n">
@@ -7639,10 +7651,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="C28" t="n">
@@ -7671,10 +7683,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C29" t="n">
@@ -7703,10 +7715,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44769</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C30" t="n">
@@ -7735,10 +7747,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C31" t="n">
@@ -7767,10 +7779,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C32" t="n">
@@ -7799,10 +7811,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45048</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="C33" t="n">
@@ -7831,10 +7843,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45134</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C34" t="n">
@@ -7863,10 +7875,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C35" t="n">
@@ -7895,10 +7907,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="C36" t="n">
@@ -7927,10 +7939,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45406</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C37" t="n">
@@ -7959,10 +7971,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C38" t="n">
@@ -7991,10 +8003,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45588</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="C39" t="n">
@@ -8023,10 +8035,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45686</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="C40" t="n">
@@ -8055,10 +8067,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45770</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C41" t="n">
@@ -8087,10 +8099,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="C42" t="n">
@@ -8119,10 +8131,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45952</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="C43" t="n">
@@ -8151,10 +8163,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46050</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="C44" t="n">
@@ -8183,10 +8195,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C45" t="n">
@@ -8233,12 +8245,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PYPL.xlsx
+++ b/salidas/empresas/PYPL.xlsx
@@ -523,7 +523,7 @@
         <v>42247</v>
       </c>
       <c r="B3" t="n">
-        <v>34.61399078369141</v>
+        <v>34.61399459838867</v>
       </c>
       <c r="C3" t="n">
         <v>35</v>
@@ -648,7 +648,7 @@
         <v>42400</v>
       </c>
       <c r="B8" t="n">
-        <v>35.74141311645508</v>
+        <v>35.74141693115234</v>
       </c>
       <c r="C8" t="n">
         <v>36.13999938964844</v>
@@ -731,7 +731,7 @@
         <v>42490</v>
       </c>
       <c r="B11" t="n">
-        <v>38.74788665771484</v>
+        <v>38.74789047241211</v>
       </c>
       <c r="C11" t="n">
         <v>39.18000030517578</v>
@@ -789,7 +789,7 @@
         <v>42551</v>
       </c>
       <c r="B13" t="n">
-        <v>36.10733795166016</v>
+        <v>36.10733413696289</v>
       </c>
       <c r="C13" t="n">
         <v>36.5099983215332</v>
@@ -818,7 +818,7 @@
         <v>42582</v>
       </c>
       <c r="B14" t="n">
-        <v>36.82928466796875</v>
+        <v>36.82928085327148</v>
       </c>
       <c r="C14" t="n">
         <v>37.2400016784668</v>
@@ -847,7 +847,7 @@
         <v>42613</v>
       </c>
       <c r="B15" t="n">
-        <v>36.74028396606445</v>
+        <v>36.74027633666992</v>
       </c>
       <c r="C15" t="n">
         <v>37.15000152587891</v>
@@ -876,7 +876,7 @@
         <v>42643</v>
       </c>
       <c r="B16" t="n">
-        <v>40.51814651489258</v>
+        <v>40.51815032958984</v>
       </c>
       <c r="C16" t="n">
         <v>40.97000122070312</v>
@@ -963,7 +963,7 @@
         <v>42735</v>
       </c>
       <c r="B19" t="n">
-        <v>39.03468704223633</v>
+        <v>39.03469467163086</v>
       </c>
       <c r="C19" t="n">
         <v>39.47000122070312</v>
@@ -1108,7 +1108,7 @@
         <v>42886</v>
       </c>
       <c r="B24" t="n">
-        <v>51.63417816162109</v>
+        <v>51.63418197631836</v>
       </c>
       <c r="C24" t="n">
         <v>52.20999908447266</v>
@@ -1137,7 +1137,7 @@
         <v>42916</v>
       </c>
       <c r="B25" t="n">
-        <v>53.07807922363281</v>
+        <v>53.07807540893555</v>
       </c>
       <c r="C25" t="n">
         <v>53.66999816894531</v>
@@ -1166,7 +1166,7 @@
         <v>42947</v>
       </c>
       <c r="B26" t="n">
-        <v>57.90425491333008</v>
+        <v>57.90425872802734</v>
       </c>
       <c r="C26" t="n">
         <v>58.54999923706055</v>
@@ -1195,7 +1195,7 @@
         <v>42978</v>
       </c>
       <c r="B27" t="n">
-        <v>60.99974060058594</v>
+        <v>60.99973678588867</v>
       </c>
       <c r="C27" t="n">
         <v>61.68000030517578</v>
@@ -1253,7 +1253,7 @@
         <v>43039</v>
       </c>
       <c r="B29" t="n">
-        <v>71.75973510742188</v>
+        <v>71.75975036621094</v>
       </c>
       <c r="C29" t="n">
         <v>72.55999755859375</v>
@@ -1282,7 +1282,7 @@
         <v>43069</v>
       </c>
       <c r="B30" t="n">
-        <v>74.894775390625</v>
+        <v>74.89479064941406</v>
       </c>
       <c r="C30" t="n">
         <v>75.73000335693359</v>
@@ -1311,7 +1311,7 @@
         <v>43100</v>
       </c>
       <c r="B31" t="n">
-        <v>72.80805206298828</v>
+        <v>72.80805969238281</v>
       </c>
       <c r="C31" t="n">
         <v>73.62000274658203</v>
@@ -1398,7 +1398,7 @@
         <v>43190</v>
       </c>
       <c r="B34" t="n">
-        <v>75.03323364257812</v>
+        <v>75.03324127197266</v>
       </c>
       <c r="C34" t="n">
         <v>75.87000274658203</v>
@@ -1456,7 +1456,7 @@
         <v>43251</v>
       </c>
       <c r="B36" t="n">
-        <v>81.16485595703125</v>
+        <v>81.16486358642578</v>
       </c>
       <c r="C36" t="n">
         <v>82.06999969482422</v>
@@ -1543,7 +1543,7 @@
         <v>43343</v>
       </c>
       <c r="B39" t="n">
-        <v>91.31169891357422</v>
+        <v>91.31170654296875</v>
       </c>
       <c r="C39" t="n">
         <v>92.33000183105469</v>
@@ -1572,7 +1572,7 @@
         <v>43373</v>
       </c>
       <c r="B40" t="n">
-        <v>86.8712158203125</v>
+        <v>86.87122344970703</v>
       </c>
       <c r="C40" t="n">
         <v>87.83999633789062</v>
@@ -1601,7 +1601,7 @@
         <v>43404</v>
       </c>
       <c r="B41" t="n">
-        <v>83.261474609375</v>
+        <v>83.26148223876953</v>
       </c>
       <c r="C41" t="n">
         <v>84.19000244140625</v>
@@ -1688,7 +1688,7 @@
         <v>43496</v>
       </c>
       <c r="B44" t="n">
-        <v>87.78107452392578</v>
+        <v>87.78108215332031</v>
       </c>
       <c r="C44" t="n">
         <v>88.76000213623047</v>
@@ -1717,7 +1717,7 @@
         <v>43524</v>
       </c>
       <c r="B45" t="n">
-        <v>96.9884033203125</v>
+        <v>96.98839569091797</v>
       </c>
       <c r="C45" t="n">
         <v>98.06999969482422</v>
@@ -1746,7 +1746,7 @@
         <v>43555</v>
       </c>
       <c r="B46" t="n">
-        <v>102.6947631835938</v>
+        <v>102.6947555541992</v>
       </c>
       <c r="C46" t="n">
         <v>103.8399963378906</v>
@@ -1862,7 +1862,7 @@
         <v>43677</v>
       </c>
       <c r="B50" t="n">
-        <v>109.1824111938477</v>
+        <v>109.1824035644531</v>
       </c>
       <c r="C50" t="n">
         <v>110.4000015258789</v>
@@ -1949,7 +1949,7 @@
         <v>43769</v>
       </c>
       <c r="B53" t="n">
-        <v>102.9518890380859</v>
+        <v>102.9518814086914</v>
       </c>
       <c r="C53" t="n">
         <v>104.0999984741211</v>
@@ -2036,7 +2036,7 @@
         <v>43861</v>
       </c>
       <c r="B56" t="n">
-        <v>112.6339263916016</v>
+        <v>112.633918762207</v>
       </c>
       <c r="C56" t="n">
         <v>113.8899993896484</v>
@@ -2181,7 +2181,7 @@
         <v>44012</v>
       </c>
       <c r="B61" t="n">
-        <v>172.3084411621094</v>
+        <v>172.3084259033203</v>
       </c>
       <c r="C61" t="n">
         <v>174.2299957275391</v>
@@ -2210,7 +2210,7 @@
         <v>44043</v>
       </c>
       <c r="B62" t="n">
-        <v>193.9075775146484</v>
+        <v>193.9075622558594</v>
       </c>
       <c r="C62" t="n">
         <v>196.0700073242188</v>
@@ -2355,7 +2355,7 @@
         <v>44196</v>
       </c>
       <c r="B67" t="n">
-        <v>231.6170196533203</v>
+        <v>231.6170349121094</v>
       </c>
       <c r="C67" t="n">
         <v>234.1999969482422</v>
@@ -2413,7 +2413,7 @@
         <v>44255</v>
       </c>
       <c r="B69" t="n">
-        <v>256.9841613769531</v>
+        <v>256.984130859375</v>
       </c>
       <c r="C69" t="n">
         <v>259.8500061035156</v>
@@ -2442,7 +2442,7 @@
         <v>44286</v>
       </c>
       <c r="B70" t="n">
-        <v>240.1617279052734</v>
+        <v>240.1617431640625</v>
       </c>
       <c r="C70" t="n">
         <v>242.8399963378906</v>
@@ -2500,7 +2500,7 @@
         <v>44347</v>
       </c>
       <c r="B72" t="n">
-        <v>257.1522827148438</v>
+        <v>257.1522521972656</v>
       </c>
       <c r="C72" t="n">
         <v>260.0199890136719</v>
@@ -2529,7 +2529,7 @@
         <v>44377</v>
       </c>
       <c r="B73" t="n">
-        <v>288.2653198242188</v>
+        <v>288.2653503417969</v>
       </c>
       <c r="C73" t="n">
         <v>291.4800109863281</v>
@@ -2558,7 +2558,7 @@
         <v>44408</v>
       </c>
       <c r="B74" t="n">
-        <v>272.4911804199219</v>
+        <v>272.4912109375</v>
       </c>
       <c r="C74" t="n">
         <v>275.5299987792969</v>
@@ -2587,7 +2587,7 @@
         <v>44439</v>
       </c>
       <c r="B75" t="n">
-        <v>285.4763793945312</v>
+        <v>285.4764099121094</v>
       </c>
       <c r="C75" t="n">
         <v>288.6600036621094</v>
@@ -2645,7 +2645,7 @@
         <v>44500</v>
       </c>
       <c r="B77" t="n">
-        <v>230.0247802734375</v>
+        <v>230.0247955322266</v>
       </c>
       <c r="C77" t="n">
         <v>232.5899963378906</v>
@@ -2674,7 +2674,7 @@
         <v>44530</v>
       </c>
       <c r="B78" t="n">
-        <v>182.8508605957031</v>
+        <v>182.8508758544922</v>
       </c>
       <c r="C78" t="n">
         <v>184.8899993896484</v>
@@ -2703,7 +2703,7 @@
         <v>44561</v>
       </c>
       <c r="B79" t="n">
-        <v>186.5001831054688</v>
+        <v>186.5001678466797</v>
       </c>
       <c r="C79" t="n">
         <v>188.5800018310547</v>
@@ -2732,7 +2732,7 @@
         <v>44592</v>
       </c>
       <c r="B80" t="n">
-        <v>170.043701171875</v>
+        <v>170.0436859130859</v>
       </c>
       <c r="C80" t="n">
         <v>171.9400024414062</v>
@@ -2790,7 +2790,7 @@
         <v>44651</v>
       </c>
       <c r="B82" t="n">
-        <v>114.3745040893555</v>
+        <v>114.37451171875</v>
       </c>
       <c r="C82" t="n">
         <v>115.6500015258789</v>
@@ -2819,7 +2819,7 @@
         <v>44681</v>
       </c>
       <c r="B83" t="n">
-        <v>86.96022033691406</v>
+        <v>86.96022796630859</v>
       </c>
       <c r="C83" t="n">
         <v>87.93000030517578</v>
@@ -2848,7 +2848,7 @@
         <v>44712</v>
       </c>
       <c r="B84" t="n">
-        <v>84.27023315429688</v>
+        <v>84.27022552490234</v>
       </c>
       <c r="C84" t="n">
         <v>85.20999908447266</v>
@@ -2877,7 +2877,7 @@
         <v>44742</v>
       </c>
       <c r="B85" t="n">
-        <v>69.06974029541016</v>
+        <v>69.06974792480469</v>
       </c>
       <c r="C85" t="n">
         <v>69.83999633789062</v>
@@ -2906,7 +2906,7 @@
         <v>44773</v>
       </c>
       <c r="B86" t="n">
-        <v>85.57567596435547</v>
+        <v>85.57566833496094</v>
       </c>
       <c r="C86" t="n">
         <v>86.52999877929688</v>
@@ -2935,7 +2935,7 @@
         <v>44804</v>
       </c>
       <c r="B87" t="n">
-        <v>92.40946960449219</v>
+        <v>92.40946197509766</v>
       </c>
       <c r="C87" t="n">
         <v>93.44000244140625</v>
@@ -2964,7 +2964,7 @@
         <v>44834</v>
       </c>
       <c r="B88" t="n">
-        <v>85.12075042724609</v>
+        <v>85.12074279785156</v>
       </c>
       <c r="C88" t="n">
         <v>86.06999969482422</v>
@@ -2993,7 +2993,7 @@
         <v>44865</v>
       </c>
       <c r="B89" t="n">
-        <v>82.65819549560547</v>
+        <v>82.658203125</v>
       </c>
       <c r="C89" t="n">
         <v>83.58000183105469</v>
@@ -3109,7 +3109,7 @@
         <v>44985</v>
       </c>
       <c r="B93" t="n">
-        <v>72.78826141357422</v>
+        <v>72.78826904296875</v>
       </c>
       <c r="C93" t="n">
         <v>73.59999847412109</v>
@@ -3138,7 +3138,7 @@
         <v>45016</v>
       </c>
       <c r="B94" t="n">
-        <v>75.10247039794922</v>
+        <v>75.10247802734375</v>
       </c>
       <c r="C94" t="n">
         <v>75.94000244140625</v>
@@ -3283,7 +3283,7 @@
         <v>45169</v>
       </c>
       <c r="B99" t="n">
-        <v>61.82058334350586</v>
+        <v>61.82057952880859</v>
       </c>
       <c r="C99" t="n">
         <v>62.5099983215332</v>
@@ -3370,7 +3370,7 @@
         <v>45260</v>
       </c>
       <c r="B102" t="n">
-        <v>56.97462463378906</v>
+        <v>56.97462844848633</v>
       </c>
       <c r="C102" t="n">
         <v>57.61000061035156</v>
@@ -3428,7 +3428,7 @@
         <v>45322</v>
       </c>
       <c r="B104" t="n">
-        <v>60.67337417602539</v>
+        <v>60.67337799072266</v>
       </c>
       <c r="C104" t="n">
         <v>61.34999847412109</v>
@@ -3457,7 +3457,7 @@
         <v>45351</v>
       </c>
       <c r="B105" t="n">
-        <v>59.67451858520508</v>
+        <v>59.67451477050781</v>
       </c>
       <c r="C105" t="n">
         <v>60.34000015258789</v>
@@ -3486,7 +3486,7 @@
         <v>45382</v>
       </c>
       <c r="B106" t="n">
-        <v>66.25116729736328</v>
+        <v>66.25117492675781</v>
       </c>
       <c r="C106" t="n">
         <v>66.98999786376953</v>
@@ -3544,7 +3544,7 @@
         <v>45443</v>
       </c>
       <c r="B108" t="n">
-        <v>62.29529571533203</v>
+        <v>62.29529190063477</v>
       </c>
       <c r="C108" t="n">
         <v>62.9900016784668</v>
@@ -3602,7 +3602,7 @@
         <v>45504</v>
       </c>
       <c r="B110" t="n">
-        <v>65.05451202392578</v>
+        <v>65.05451965332031</v>
       </c>
       <c r="C110" t="n">
         <v>65.77999877929688</v>
@@ -3631,7 +3631,7 @@
         <v>45535</v>
       </c>
       <c r="B111" t="n">
-        <v>71.63117218017578</v>
+        <v>71.63117980957031</v>
       </c>
       <c r="C111" t="n">
         <v>72.43000030517578</v>
@@ -3689,7 +3689,7 @@
         <v>45596</v>
       </c>
       <c r="B113" t="n">
-        <v>78.42540740966797</v>
+        <v>78.4254150390625</v>
       </c>
       <c r="C113" t="n">
         <v>79.30000305175781</v>
@@ -3805,7 +3805,7 @@
         <v>45716</v>
       </c>
       <c r="B117" t="n">
-        <v>70.26639556884766</v>
+        <v>70.26640319824219</v>
       </c>
       <c r="C117" t="n">
         <v>71.05000305175781</v>
@@ -3863,7 +3863,7 @@
         <v>45777</v>
       </c>
       <c r="B119" t="n">
-        <v>65.11386108398438</v>
+        <v>65.11385345458984</v>
       </c>
       <c r="C119" t="n">
         <v>65.83999633789062</v>
@@ -3892,7 +3892,7 @@
         <v>45808</v>
       </c>
       <c r="B120" t="n">
-        <v>69.50489044189453</v>
+        <v>69.5048828125</v>
       </c>
       <c r="C120" t="n">
         <v>70.27999877929688</v>
@@ -3921,7 +3921,7 @@
         <v>45838</v>
       </c>
       <c r="B121" t="n">
-        <v>73.50033569335938</v>
+        <v>73.50032806396484</v>
       </c>
       <c r="C121" t="n">
         <v>74.31999969482422</v>
@@ -3950,7 +3950,7 @@
         <v>45869</v>
       </c>
       <c r="B122" t="n">
-        <v>68.00166320800781</v>
+        <v>68.00165557861328</v>
       </c>
       <c r="C122" t="n">
         <v>68.76000213623047</v>
@@ -3979,7 +3979,7 @@
         <v>45900</v>
       </c>
       <c r="B123" t="n">
-        <v>69.4158935546875</v>
+        <v>69.41588592529297</v>
       </c>
       <c r="C123" t="n">
         <v>70.19000244140625</v>
@@ -4008,7 +4008,7 @@
         <v>45930</v>
       </c>
       <c r="B124" t="n">
-        <v>66.32039642333984</v>
+        <v>66.32040405273438</v>
       </c>
       <c r="C124" t="n">
         <v>67.05999755859375</v>
